--- a/reports/web_e2e_report.xlsx
+++ b/reports/web_e2e_report.xlsx
@@ -51,66 +51,48 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr" s="1">
-        <is>
-          <t>Metric</t>
-        </is>
+      <c r="A1" t="str" s="1">
+        <v>Metric</v>
       </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t>Value</t>
-        </is>
+      <c r="B1" t="str" s="1">
+        <v>Value</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
+      <c r="A2" t="str">
+        <v>status</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
+      <c r="B2" t="str">
+        <v>PASSED</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>suite</t>
-        </is>
+      <c r="A3" t="str">
+        <v>suite</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TravelSync Web E2E Tests</t>
-        </is>
+      <c r="B3" t="str">
+        <v>TravelSync Web E2E Tests</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
+      <c r="A4" t="str">
+        <v>total</v>
       </c>
       <c r="B4" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>passed</t>
-        </is>
+      <c r="A5" t="str">
+        <v>passed</v>
       </c>
       <c r="B5" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
+      <c r="A6" t="str">
+        <v>failed</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
